--- a/public/template/排班工具配置模板.xlsx
+++ b/public/template/排班工具配置模板.xlsx
@@ -139,10 +139,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -173,10 +173,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -950,7 +950,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="20"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -960,6 +960,7 @@
     <col min="6" max="6" customWidth="1" width="14"/>
     <col min="7" max="7" customWidth="1" width="14.83203125"/>
     <col min="8" max="8" customWidth="1" width="14.83203125"/>
+    <col min="9" max="9" customWidth="1" width="16.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -987,6 +988,9 @@
       <c r="H1" s="3" t="str">
         <v>值班资质</v>
       </c>
+      <c r="I1" s="3" t="str">
+        <v>是否为分队长</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="str">
@@ -1010,6 +1014,9 @@
       <c r="H2" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I2" s="3" t="str">
+        <v>是</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="str">
@@ -1033,6 +1040,9 @@
       <c r="H3" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I3" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="str">
@@ -1056,6 +1066,9 @@
       <c r="H4" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I4" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="str">
@@ -1079,6 +1092,9 @@
       <c r="H5" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I5" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="str">
@@ -1102,6 +1118,9 @@
       <c r="H6" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I6" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="str">
@@ -1125,6 +1144,9 @@
       <c r="H7" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I7" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="str">
@@ -1148,6 +1170,9 @@
       <c r="H8" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I8" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="str">
@@ -1171,6 +1196,9 @@
       <c r="H9" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I9" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="str">
@@ -1194,6 +1222,9 @@
       <c r="H10" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I10" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="str">
@@ -1217,6 +1248,9 @@
       <c r="H11" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I11" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="str">
@@ -1240,6 +1274,9 @@
       <c r="H12" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I12" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="str">
@@ -1263,6 +1300,9 @@
       <c r="H13" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I13" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="str">
@@ -1286,6 +1326,9 @@
       <c r="H14" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I14" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="str">
@@ -1309,6 +1352,9 @@
       <c r="H15" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I15" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="str">
@@ -1332,6 +1378,9 @@
       <c r="H16" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I16" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="str">
@@ -1358,6 +1407,9 @@
       <c r="H17" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I17" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="str">
@@ -1384,6 +1436,9 @@
       <c r="H18" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I18" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="str">
@@ -1410,11 +1465,14 @@
       <c r="H19" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="I19" s="3" t="str">
+        <v>否</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/template/排班工具配置模板.xlsx
+++ b/public/template/排班工具配置模板.xlsx
@@ -139,10 +139,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -173,10 +173,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -950,7 +950,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="20"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -960,7 +960,8 @@
     <col min="6" max="6" customWidth="1" width="14"/>
     <col min="7" max="7" customWidth="1" width="14.83203125"/>
     <col min="8" max="8" customWidth="1" width="14.83203125"/>
-    <col min="9" max="9" customWidth="1" width="16.83203125"/>
+    <col min="9" max="9" customWidth="1" width="14.83203125"/>
+    <col min="10" max="10" customWidth="1" width="16.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -989,6 +990,9 @@
         <v>值班资质</v>
       </c>
       <c r="I1" s="3" t="str">
+        <v>备勤资质</v>
+      </c>
+      <c r="J1" s="3" t="str">
         <v>是否为分队长</v>
       </c>
     </row>
@@ -1017,6 +1021,9 @@
       <c r="I2" s="3" t="str">
         <v>是</v>
       </c>
+      <c r="J2" s="3" t="str">
+        <v>是</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="str">
@@ -1041,6 +1048,9 @@
         <v>是</v>
       </c>
       <c r="I3" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J3" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1067,6 +1077,9 @@
         <v>是</v>
       </c>
       <c r="I4" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J4" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1093,6 +1106,9 @@
         <v>是</v>
       </c>
       <c r="I5" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J5" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1119,6 +1135,9 @@
         <v>是</v>
       </c>
       <c r="I6" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J6" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1145,6 +1164,9 @@
         <v>是</v>
       </c>
       <c r="I7" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J7" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1171,6 +1193,9 @@
         <v>是</v>
       </c>
       <c r="I8" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J8" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1197,6 +1222,9 @@
         <v>是</v>
       </c>
       <c r="I9" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J9" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1223,6 +1251,9 @@
         <v>是</v>
       </c>
       <c r="I10" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J10" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1249,6 +1280,9 @@
         <v>是</v>
       </c>
       <c r="I11" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J11" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1275,6 +1309,9 @@
         <v>是</v>
       </c>
       <c r="I12" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J12" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1301,6 +1338,9 @@
         <v>是</v>
       </c>
       <c r="I13" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J13" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1327,6 +1367,9 @@
         <v>是</v>
       </c>
       <c r="I14" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J14" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1353,6 +1396,9 @@
         <v>是</v>
       </c>
       <c r="I15" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J15" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1379,6 +1425,9 @@
         <v>是</v>
       </c>
       <c r="I16" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J16" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1408,6 +1457,9 @@
         <v>是</v>
       </c>
       <c r="I17" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J17" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1437,6 +1489,9 @@
         <v>是</v>
       </c>
       <c r="I18" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J18" s="3" t="str">
         <v>否</v>
       </c>
     </row>
@@ -1466,13 +1521,16 @@
         <v>是</v>
       </c>
       <c r="I19" s="3" t="str">
+        <v>是</v>
+      </c>
+      <c r="J19" s="3" t="str">
         <v>否</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/template/排班工具配置模板.xlsx
+++ b/public/template/排班工具配置模板.xlsx
@@ -6,15 +6,17 @@
     <sheet name="人员信息" sheetId="1" r:id="rId1"/>
     <sheet name="航班计划" sheetId="2" r:id="rId2"/>
     <sheet name="航班配置" sheetId="3" r:id="rId3"/>
-    <sheet name="岗位配置" sheetId="4" r:id="rId4"/>
-    <sheet name="规则参数" sheetId="5" r:id="rId5"/>
-    <sheet name="岗位衔接规则" sheetId="6" r:id="rId6"/>
-    <sheet name="值班岗位优先" sheetId="7" r:id="rId7"/>
-    <sheet name="次班恢复目标" sheetId="8" r:id="rId8"/>
-    <sheet name="末班重点岗位" sheetId="9" r:id="rId9"/>
-    <sheet name="机动督导范围" sheetId="10" r:id="rId10"/>
-    <sheet name="跨工作日资质预留" sheetId="11" r:id="rId11"/>
-    <sheet name="末班重点航班范围" sheetId="12" r:id="rId12"/>
+    <sheet name="每周航班计划" sheetId="4" r:id="rId4"/>
+    <sheet name="岗位配置" sheetId="5" r:id="rId5"/>
+    <sheet name="规则参数" sheetId="6" r:id="rId6"/>
+    <sheet name="岗位衔接规则" sheetId="7" r:id="rId7"/>
+    <sheet name="值班岗位优先" sheetId="8" r:id="rId8"/>
+    <sheet name="次班恢复目标" sheetId="9" r:id="rId9"/>
+    <sheet name="末班重点岗位" sheetId="10" r:id="rId10"/>
+    <sheet name="机动督导范围" sheetId="11" r:id="rId11"/>
+    <sheet name="跨工作日资质预留" sheetId="12" r:id="rId12"/>
+    <sheet name="末班重点航班范围" sheetId="13" r:id="rId13"/>
+    <sheet name="跨航班重点岗位优先" sheetId="14" r:id="rId14"/>
   </sheets>
 </workbook>
 </file>
@@ -1051,6 +1053,125 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>规则ID</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>启用</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>航班号（空白表示全部）</v>
+      </c>
+      <c r="D1" s="2" t="str">
+        <v>匹配字段</v>
+      </c>
+      <c r="E1" s="2" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="F1" s="2" t="str">
+        <v>次班截止时间（可留空）</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>late-recovery-supervisor</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>是</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>position</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>督导</v>
+      </c>
+      <c r="F2" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>late-recovery-one</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>是</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D3" s="2" t="str">
+        <v>remark</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <v>一号</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>late-recovery-declaration</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>是</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D4" s="2" t="str">
+        <v>remark</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <v>申报</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>late-recovery-delivery</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>是</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D5" s="2" t="str">
+        <v>remark</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <v>送资料</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -1148,7 +1269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F1"/>
   <cols>
@@ -1187,7 +1308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <cols>
@@ -1222,6 +1343,37 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D1"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>规则ID</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>启用</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>优先航班号</v>
+      </c>
+      <c r="D1" s="2" t="str">
+        <v>优先岗位（逗号分隔）</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1450,6 +1602,85 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="48.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>星期</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>航班号（用逗号分隔）</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>星期一</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>星期二</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>星期三</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>星期四</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>星期五</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>星期六</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="str">
+        <v>星期日</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H40"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
@@ -2509,9 +2740,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -2745,138 +2976,152 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="str">
-        <v>lateShiftEndTime</v>
+        <v>nextWorkdayRecoveryMode</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>末班结束界线</v>
+        <v>跨工作日恢复目标强度</v>
       </c>
       <c r="C17" s="2" t="str">
-        <v>23:00</v>
+        <v>prefer</v>
       </c>
       <c r="D17" s="2" t="str">
-        <v>实际结束时间晚于该时刻的重点岗位纳入末班统计</v>
+        <v>优先避开或严格限制次班恢复目标</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="str">
-        <v>teamLeaderConcurrentSupervisionMaxOverlapMinutes</v>
+        <v>lateShiftEndTime</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>分队长并行督导最大重叠分钟</v>
-      </c>
-      <c r="C18" s="2">
-        <v>30</v>
+        <v>末班结束界线</v>
+      </c>
+      <c r="C18" s="2" t="str">
+        <v>23:00</v>
       </c>
       <c r="D18" s="2" t="str">
-        <v>只在补齐常规岗位空缺时允许两个督导原始保障时段重叠的上限</v>
+        <v>实际结束时间晚于该时刻的重点岗位纳入末班统计</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="str">
-        <v>dutyFatiguePoints</v>
+        <v>teamLeaderConcurrentSupervisionMaxOverlapMinutes</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>值班疲劳点数</v>
+        <v>分队长并行督导最大重叠分钟</v>
       </c>
       <c r="C19" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D19" s="2" t="str">
-        <v>值班任务计入的疲劳点</v>
+        <v>只在补齐常规岗位空缺时允许两个督导原始保障时段重叠的上限</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="str">
-        <v>earlyDepartureCutoffTime</v>
+        <v>dutyFatiguePoints</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>提前下班截载节点</v>
-      </c>
-      <c r="C20" s="2" t="str">
-        <v>12:00</v>
+        <v>值班疲劳点数</v>
+      </c>
+      <c r="C20" s="2">
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="str">
-        <v>严格早于该时间计提前下班</v>
+        <v>值班任务计入的疲劳点</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="str">
-        <v>afternoonRestStartTime</v>
+        <v>earlyDepartureCutoffTime</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>下午无航班开始</v>
+        <v>提前下班截载节点</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>12:00</v>
       </c>
       <c r="D21" s="2" t="str">
-        <v>下午无航班统计起点</v>
+        <v>严格早于该时间计提前下班</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="str">
-        <v>afternoonRestEndTime</v>
+        <v>afternoonRestStartTime</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>下午无航班结束</v>
+        <v>下午无航班开始</v>
       </c>
       <c r="C22" s="2" t="str">
-        <v>18:00</v>
+        <v>12:00</v>
       </c>
       <c r="D22" s="2" t="str">
-        <v>下午无航班统计终点</v>
+        <v>下午无航班统计起点</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="str">
-        <v>workloadBalanceEnabled</v>
+        <v>afternoonRestEndTime</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>启用工时疲劳均衡</v>
+        <v>下午无航班结束</v>
       </c>
       <c r="C23" s="2" t="str">
-        <v>是</v>
+        <v>18:00</v>
       </c>
       <c r="D23" s="2" t="str">
-        <v>是否执行人员负荷均衡</v>
+        <v>下午无航班统计终点</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="str">
-        <v>maxWorkHoursDifference</v>
+        <v>workloadBalanceEnabled</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>最大工时差</v>
-      </c>
-      <c r="C24" s="2">
-        <v>2</v>
+        <v>启用工时疲劳均衡</v>
+      </c>
+      <c r="C24" s="2" t="str">
+        <v>是</v>
       </c>
       <c r="D24" s="2" t="str">
-        <v>常规人员当日工时差目标</v>
+        <v>是否执行人员负荷均衡</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="str">
+        <v>maxWorkHoursDifference</v>
+      </c>
+      <c r="B25" s="2" t="str">
+        <v>最大工时差</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2" t="str">
+        <v>常规人员当日工时差目标</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="str">
         <v>maxTodayFatigueDifference</v>
       </c>
-      <c r="B25" s="2" t="str">
+      <c r="B26" s="2" t="str">
         <v>最大当日疲劳差</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C26" s="2">
         <v>4</v>
       </c>
-      <c r="D25" s="2" t="str">
+      <c r="D26" s="2" t="str">
         <v>常规人员当日疲劳差目标</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D26"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
   <cols>
@@ -2956,7 +3201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <cols>
@@ -3015,7 +3260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <cols>
@@ -3086,123 +3331,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <cols>
-    <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="24.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="str">
-        <v>规则ID</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <v>启用</v>
-      </c>
-      <c r="C1" s="2" t="str">
-        <v>航班号（空白表示全部）</v>
-      </c>
-      <c r="D1" s="2" t="str">
-        <v>匹配字段</v>
-      </c>
-      <c r="E1" s="2" t="str">
-        <v>关键词</v>
-      </c>
-      <c r="F1" s="2" t="str">
-        <v>次班截止时间（可留空）</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="str">
-        <v>late-recovery-supervisor</v>
-      </c>
-      <c r="B2" s="2" t="str">
-        <v>是</v>
-      </c>
-      <c r="C2" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D2" s="2" t="str">
-        <v>position</v>
-      </c>
-      <c r="E2" s="2" t="str">
-        <v>督导</v>
-      </c>
-      <c r="F2" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="str">
-        <v>late-recovery-one</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>是</v>
-      </c>
-      <c r="C3" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D3" s="2" t="str">
-        <v>remark</v>
-      </c>
-      <c r="E3" s="2" t="str">
-        <v>一号</v>
-      </c>
-      <c r="F3" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="str">
-        <v>late-recovery-declaration</v>
-      </c>
-      <c r="B4" s="2" t="str">
-        <v>是</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D4" s="2" t="str">
-        <v>remark</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v>申报</v>
-      </c>
-      <c r="F4" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="str">
-        <v>late-recovery-delivery</v>
-      </c>
-      <c r="B5" s="2" t="str">
-        <v>是</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D5" s="2" t="str">
-        <v>remark</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v>送资料</v>
-      </c>
-      <c r="F5" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
-  </ignoredErrors>
-</worksheet>
 </file>